--- a/Data/DOM_remineralization.xlsx
+++ b/Data/DOM_remineralization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanceenglish/Desktop/Lab Shiz/ARPA-e/MP Exudate Sampling/data/Compiled Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chanceenglish/Desktop/Lab Shiz/ARPA-e/Giant_Kelp_DOC/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD7DBF23-36CA-DB48-AC89-BBFC817C2136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21206EF5-63F9-AA43-9449-0481BD72899E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{57C09377-839F-C344-BC84-8B89784BD3D1}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{57C09377-839F-C344-BC84-8B89784BD3D1}"/>
   </bookViews>
   <sheets>
     <sheet name="DOC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="152">
   <si>
     <t>days</t>
   </si>
@@ -423,6 +423,78 @@
   </si>
   <si>
     <t>MPExudate_20240528 B6 T3</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B0 T0</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B0 T1</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B0 T2</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B0 T3</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B1 T0</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B1 T1</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B1 T2</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B1 T3</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B3 T0</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B3 T1</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B3 T2</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B3 T3</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B4 T0</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B4 T1</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B4 T2</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B4 T3</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B5 T0</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B5 T1</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B5 T2</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B5 T3</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B6 T0</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B6 T1</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B6 T2</t>
+  </si>
+  <si>
+    <t>MPExudate_20240415-A3 B6 T3</t>
   </si>
 </sst>
 </file>
@@ -487,1328 +559,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>16</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>DOC!$K$26:$K$32</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>66.017586609100036</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>62.551485632787397</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>59.620773467994468</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>58.705764073354779</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>81.259146705832038</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>70.817001725854396</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>62.750580123391067</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>DOC!$N$26:$N$32</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0.86706520979494595</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.972813389648852</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.9145062952659599</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-707F-5D44-990E-BBE038D26544}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:v>14</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>DOC!$K$2:$K$6</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>58.176404986182824</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>58.487224879079349</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>57.847635008286204</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>56.8717172290701</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>75.13829056996407</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>DOC!$N$2:$N$6</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1.05932498107233</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0427511142805199</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.04165701074142</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.0185105942841599</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.90620063300536</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-707F-5D44-990E-BBE038D26544}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:v>37</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>DOC!$K$54:$K$60</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>55.180604655866269</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>54.260060201019257</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>53.373768563096768</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>52.507814535223226</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>69.185725175887782</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>62.94529009244804</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>58.358623826146307</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>DOC!$N$54:$N$60</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0.92133000539282595</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.89790035973058202</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.38421498569372</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-707F-5D44-990E-BBE038D26544}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:v>all</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="25400" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-9.9961282464001391E-2"/>
-                  <c:y val="-1.9496137804627153E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>(DOC!$K$2:$K$6,DOC!$K$26:$K$32,DOC!$K$54:$K$60)</c:f>
-              <c:numCache>
-                <c:formatCode>0.0</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>58.176404986182824</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>58.487224879079349</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>57.847635008286204</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>56.8717172290701</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>75.13829056996407</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>66.017586609100036</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>62.551485632787397</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>59.620773467994468</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>58.705764073354779</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>81.259146705832038</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>70.817001725854396</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>62.750580123391067</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>55.180604655866269</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>54.260060201019257</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>53.373768563096768</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>52.507814535223226</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>69.185725175887782</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>62.94529009244804</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>58.358623826146307</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>(DOC!$N$2:$N$6,DOC!$N$26:$N$32,DOC!$N$54:$N$60)</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="19"/>
-                <c:pt idx="0">
-                  <c:v>1.05932498107233</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.0427511142805199</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.04165701074142</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.0185105942841599</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.90620063300536</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.86706520979494595</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.972813389648852</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.9145062952659599</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.92133000539282595</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.89790035973058202</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.38421498569372</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000007-707F-5D44-990E-BBE038D26544}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1654163440"/>
-        <c:axId val="1650965776"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1654163440"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1650965776"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1650965776"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1654163440"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>215900</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{205FC27E-07FD-F02E-8B57-D3BD45B0D117}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1846,7 +600,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1952,7 +706,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2094,7 +848,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2105,7 +859,7 @@
   <dimension ref="A1:Q139"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="3"/>
     <col min="6" max="6" width="10.83203125" style="4"/>
@@ -2183,7 +937,7 @@
         <v>0.75</v>
       </c>
       <c r="G2" s="2">
-        <f>_xlfn.DAYS(E2,$E$2)</f>
+        <f t="shared" ref="G2:G25" si="0">_xlfn.DAYS(E2,$E$2)</f>
         <v>0</v>
       </c>
       <c r="H2">
@@ -2208,7 +962,7 @@
         <v>1.05932498107233</v>
       </c>
       <c r="O2" s="5">
-        <f>N2/K2</f>
+        <f t="shared" ref="O2:O26" si="1">N2/K2</f>
         <v>1.8208842250117117E-2</v>
       </c>
       <c r="Q2" s="2"/>
@@ -2233,7 +987,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="G3" s="2">
-        <f>_xlfn.DAYS(E3,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="H3">
@@ -2258,7 +1012,7 @@
         <v>1.0427511142805199</v>
       </c>
       <c r="O3" s="5">
-        <f>N3/K3</f>
+        <f t="shared" si="1"/>
         <v>1.7828698770310573E-2</v>
       </c>
     </row>
@@ -2282,7 +1036,7 @@
         <v>0.5</v>
       </c>
       <c r="G4" s="2">
-        <f>_xlfn.DAYS(E4,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H4">
@@ -2307,7 +1061,7 @@
         <v>1.04165701074142</v>
       </c>
       <c r="O4" s="5">
-        <f>N4/K4</f>
+        <f t="shared" si="1"/>
         <v>1.8006907466350371E-2</v>
       </c>
     </row>
@@ -2331,7 +1085,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G5" s="2">
-        <f>_xlfn.DAYS(E5,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="H5">
@@ -2356,7 +1110,7 @@
         <v>1.0185105942841599</v>
       </c>
       <c r="O5" s="5">
-        <f>N5/K5</f>
+        <f t="shared" si="1"/>
         <v>1.7908912266210698E-2</v>
       </c>
     </row>
@@ -2380,7 +1134,7 @@
         <v>0.75</v>
       </c>
       <c r="G6" s="2">
-        <f>_xlfn.DAYS(E6,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6">
@@ -2405,7 +1159,7 @@
         <v>1.90620063300536</v>
       </c>
       <c r="O6" s="5">
-        <f>N6/K6</f>
+        <f t="shared" si="1"/>
         <v>2.5369230768304815E-2</v>
       </c>
     </row>
@@ -2429,7 +1183,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="G7" s="2">
-        <f>_xlfn.DAYS(E7,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="H7">
@@ -2454,7 +1208,7 @@
         <v>1.85228501222488</v>
       </c>
       <c r="O7" s="5">
-        <f>N7/K7</f>
+        <f t="shared" si="1"/>
         <v>2.7191577379509755E-2</v>
       </c>
     </row>
@@ -2478,7 +1232,7 @@
         <v>0.5</v>
       </c>
       <c r="G8" s="2">
-        <f>_xlfn.DAYS(E8,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H8">
@@ -2503,7 +1257,7 @@
         <v>1.79082799947928</v>
       </c>
       <c r="O8" s="5">
-        <f>N8/K8</f>
+        <f t="shared" si="1"/>
         <v>2.8278999352531049E-2</v>
       </c>
     </row>
@@ -2527,7 +1281,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G9" s="2">
-        <f>_xlfn.DAYS(E9,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="H9">
@@ -2552,7 +1306,7 @@
         <v>1.6896312011383201</v>
       </c>
       <c r="O9" s="5">
-        <f>N9/K9</f>
+        <f t="shared" si="1"/>
         <v>2.6820641278097166E-2</v>
       </c>
     </row>
@@ -2576,7 +1330,7 @@
         <v>0.75</v>
       </c>
       <c r="G10" s="2">
-        <f>_xlfn.DAYS(E10,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H10">
@@ -2601,7 +1355,7 @@
         <v>1.81839308185644</v>
       </c>
       <c r="O10" s="5">
-        <f>N10/K10</f>
+        <f t="shared" si="1"/>
         <v>1.9411709832586072E-2</v>
       </c>
     </row>
@@ -2625,7 +1379,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="G11" s="2">
-        <f>_xlfn.DAYS(E11,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="H11">
@@ -2650,7 +1404,7 @@
         <v>1.8342600433774301</v>
       </c>
       <c r="O11" s="5">
-        <f>N11/K11</f>
+        <f t="shared" si="1"/>
         <v>2.3601654614994704E-2</v>
       </c>
     </row>
@@ -2674,7 +1428,7 @@
         <v>0.5</v>
       </c>
       <c r="G12" s="2">
-        <f>_xlfn.DAYS(E12,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H12">
@@ -2699,7 +1453,7 @@
         <v>1.7475458487420901</v>
       </c>
       <c r="O12" s="5">
-        <f>N12/K12</f>
+        <f t="shared" si="1"/>
         <v>2.687817659097351E-2</v>
       </c>
     </row>
@@ -2723,7 +1477,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G13" s="2">
-        <f>_xlfn.DAYS(E13,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="H13">
@@ -2748,7 +1502,7 @@
         <v>1.64515365020133</v>
       </c>
       <c r="O13" s="5">
-        <f>N13/K13</f>
+        <f t="shared" si="1"/>
         <v>2.6642823693411456E-2</v>
       </c>
     </row>
@@ -2772,7 +1526,7 @@
         <v>0.75</v>
       </c>
       <c r="G14" s="2">
-        <f>_xlfn.DAYS(E14,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H14">
@@ -2797,7 +1551,7 @@
         <v>1.8734027553782799</v>
       </c>
       <c r="O14" s="5">
-        <f>N14/K14</f>
+        <f t="shared" si="1"/>
         <v>2.4540182824255994E-2</v>
       </c>
     </row>
@@ -2821,7 +1575,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="G15" s="2">
-        <f>_xlfn.DAYS(E15,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="H15">
@@ -2846,7 +1600,7 @@
         <v>1.8069020429490501</v>
       </c>
       <c r="O15" s="5">
-        <f>N15/K15</f>
+        <f t="shared" si="1"/>
         <v>2.5080110482865851E-2</v>
       </c>
     </row>
@@ -2870,7 +1624,7 @@
         <v>0.5</v>
       </c>
       <c r="G16" s="2">
-        <f>_xlfn.DAYS(E16,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H16">
@@ -2895,7 +1649,7 @@
         <v>1.7119153658775099</v>
       </c>
       <c r="O16" s="5">
-        <f>N16/K16</f>
+        <f t="shared" si="1"/>
         <v>2.7083277169974176E-2</v>
       </c>
     </row>
@@ -2919,7 +1673,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G17" s="2">
-        <f>_xlfn.DAYS(E17,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="H17">
@@ -2944,7 +1698,7 @@
         <v>1.57625606803911</v>
       </c>
       <c r="O17" s="5">
-        <f>N17/K17</f>
+        <f t="shared" si="1"/>
         <v>2.5862549055253224E-2</v>
       </c>
     </row>
@@ -2968,7 +1722,7 @@
         <v>0.75</v>
       </c>
       <c r="G18" s="2">
-        <f>_xlfn.DAYS(E18,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H18">
@@ -2993,7 +1747,7 @@
         <v>1.8314918382141001</v>
       </c>
       <c r="O18" s="5">
-        <f>N18/K18</f>
+        <f t="shared" si="1"/>
         <v>2.4102831281504505E-2</v>
       </c>
     </row>
@@ -3017,7 +1771,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="G19" s="2">
-        <f>_xlfn.DAYS(E19,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="H19">
@@ -3042,7 +1796,7 @@
         <v>1.776579774035</v>
       </c>
       <c r="O19" s="5">
-        <f>N19/K19</f>
+        <f t="shared" si="1"/>
         <v>2.5448775327633538E-2</v>
       </c>
     </row>
@@ -3066,7 +1820,7 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="2">
-        <f>_xlfn.DAYS(E20,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H20">
@@ -3091,7 +1845,7 @@
         <v>1.6491249877766301</v>
       </c>
       <c r="O20" s="5">
-        <f>N20/K20</f>
+        <f t="shared" si="1"/>
         <v>2.6624279938887028E-2</v>
       </c>
     </row>
@@ -3115,7 +1869,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G21" s="2">
-        <f>_xlfn.DAYS(E21,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="H21">
@@ -3140,7 +1894,7 @@
         <v>1.5308922510036</v>
       </c>
       <c r="O21" s="5">
-        <f>N21/K21</f>
+        <f t="shared" si="1"/>
         <v>2.5872044314382836E-2</v>
       </c>
     </row>
@@ -3164,7 +1918,7 @@
         <v>0.75</v>
       </c>
       <c r="G22" s="2">
-        <f>_xlfn.DAYS(E22,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H22">
@@ -3189,7 +1943,7 @@
         <v>1.5788359495625299</v>
       </c>
       <c r="O22" s="5">
-        <f>N22/K22</f>
+        <f t="shared" si="1"/>
         <v>2.2072204488561883E-2</v>
       </c>
     </row>
@@ -3213,7 +1967,7 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="G23" s="2">
-        <f>_xlfn.DAYS(E23,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="H23">
@@ -3238,7 +1992,7 @@
         <v>1.55670315609882</v>
       </c>
       <c r="O23" s="5">
-        <f>N23/K23</f>
+        <f t="shared" si="1"/>
         <v>2.3813667874506339E-2</v>
       </c>
     </row>
@@ -3262,7 +2016,7 @@
         <v>0.5</v>
       </c>
       <c r="G24" s="2">
-        <f>_xlfn.DAYS(E24,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="H24">
@@ -3287,7 +2041,7 @@
         <v>1.41126474387545</v>
       </c>
       <c r="O24" s="5">
-        <f>N24/K24</f>
+        <f t="shared" si="1"/>
         <v>2.3884199337054931E-2</v>
       </c>
     </row>
@@ -3311,7 +2065,7 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="G25" s="2">
-        <f>_xlfn.DAYS(E25,$E$2)</f>
+        <f t="shared" si="0"/>
         <v>92</v>
       </c>
       <c r="H25">
@@ -3336,7 +2090,7 @@
         <v>1.3105007810859499</v>
       </c>
       <c r="O25" s="5">
-        <f>N25/K25</f>
+        <f t="shared" si="1"/>
         <v>2.2145320515655355E-2</v>
       </c>
     </row>
@@ -3360,7 +2114,7 @@
         <v>0.625</v>
       </c>
       <c r="G26" s="2">
-        <f>_xlfn.DAYS(E26,$E$26)</f>
+        <f t="shared" ref="G26:G53" si="2">_xlfn.DAYS(E26,$E$26)</f>
         <v>0</v>
       </c>
       <c r="H26">
@@ -3385,7 +2139,7 @@
         <v>0.86706520979494595</v>
       </c>
       <c r="O26" s="5">
-        <f>N26/K26</f>
+        <f t="shared" si="1"/>
         <v>1.31338519677941E-2</v>
       </c>
     </row>
@@ -3409,7 +2163,7 @@
         <v>0.53125</v>
       </c>
       <c r="G27" s="2">
-        <f>_xlfn.DAYS(E27,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H27">
@@ -3451,7 +2205,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G28" s="2">
-        <f>_xlfn.DAYS(E28,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="H28">
@@ -3493,7 +2247,7 @@
         <v>0.5</v>
       </c>
       <c r="G29" s="2">
-        <f>_xlfn.DAYS(E29,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="H29">
@@ -3542,7 +2296,7 @@
         <v>0.625</v>
       </c>
       <c r="G30" s="2">
-        <f>_xlfn.DAYS(E30,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H30">
@@ -3591,7 +2345,7 @@
         <v>0.53125</v>
       </c>
       <c r="G31" s="2">
-        <f>_xlfn.DAYS(E31,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H31">
@@ -3633,7 +2387,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G32" s="2">
-        <f>_xlfn.DAYS(E32,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="H32">
@@ -3675,7 +2429,7 @@
         <v>0.5</v>
       </c>
       <c r="G33" s="2">
-        <f>_xlfn.DAYS(E33,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="H33">
@@ -3724,7 +2478,7 @@
         <v>0.625</v>
       </c>
       <c r="G34" s="2">
-        <f>_xlfn.DAYS(E34,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H34">
@@ -3773,7 +2527,7 @@
         <v>0.53125</v>
       </c>
       <c r="G35" s="2">
-        <f>_xlfn.DAYS(E35,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H35">
@@ -3815,7 +2569,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G36" s="2">
-        <f>_xlfn.DAYS(E36,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="H36">
@@ -3857,7 +2611,7 @@
         <v>0.5</v>
       </c>
       <c r="G37" s="2">
-        <f>_xlfn.DAYS(E37,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="H37">
@@ -3906,7 +2660,7 @@
         <v>0.625</v>
       </c>
       <c r="G38" s="2">
-        <f>_xlfn.DAYS(E38,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H38">
@@ -3955,7 +2709,7 @@
         <v>0.53125</v>
       </c>
       <c r="G39" s="2">
-        <f>_xlfn.DAYS(E39,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H39">
@@ -3997,7 +2751,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G40" s="2">
-        <f>_xlfn.DAYS(E40,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="H40">
@@ -4039,7 +2793,7 @@
         <v>0.5</v>
       </c>
       <c r="G41" s="2">
-        <f>_xlfn.DAYS(E41,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="H41">
@@ -4088,7 +2842,7 @@
         <v>0.625</v>
       </c>
       <c r="G42" s="2">
-        <f>_xlfn.DAYS(E42,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H42">
@@ -4137,7 +2891,7 @@
         <v>0.53125</v>
       </c>
       <c r="G43" s="2">
-        <f>_xlfn.DAYS(E43,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H43">
@@ -4179,7 +2933,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G44" s="2">
-        <f>_xlfn.DAYS(E44,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="H44">
@@ -4221,7 +2975,7 @@
         <v>0.5</v>
       </c>
       <c r="G45" s="2">
-        <f>_xlfn.DAYS(E45,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="H45">
@@ -4270,7 +3024,7 @@
         <v>0.625</v>
       </c>
       <c r="G46" s="2">
-        <f>_xlfn.DAYS(E46,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H46">
@@ -4319,7 +3073,7 @@
         <v>0.53125</v>
       </c>
       <c r="G47" s="2">
-        <f>_xlfn.DAYS(E47,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H47">
@@ -4361,7 +3115,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G48" s="2">
-        <f>_xlfn.DAYS(E48,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="H48">
@@ -4403,7 +3157,7 @@
         <v>0.5</v>
       </c>
       <c r="G49" s="2">
-        <f>_xlfn.DAYS(E49,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="H49">
@@ -4452,7 +3206,7 @@
         <v>0.625</v>
       </c>
       <c r="G50" s="2">
-        <f>_xlfn.DAYS(E50,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H50">
@@ -4501,7 +3255,7 @@
         <v>0.53125</v>
       </c>
       <c r="G51" s="2">
-        <f>_xlfn.DAYS(E51,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="H51">
@@ -4543,7 +3297,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G52" s="2">
-        <f>_xlfn.DAYS(E52,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="H52">
@@ -4585,7 +3339,7 @@
         <v>0.5</v>
       </c>
       <c r="G53" s="2">
-        <f>_xlfn.DAYS(E53,$E$26)</f>
+        <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="H53">
@@ -4634,7 +3388,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G54" s="2">
-        <f>_xlfn.DAYS(E54,$E$54)</f>
+        <f t="shared" ref="G54:G81" si="3">_xlfn.DAYS(E54,$E$54)</f>
         <v>0</v>
       </c>
       <c r="H54">
@@ -4683,7 +3437,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G55" s="2">
-        <f>_xlfn.DAYS(E55,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H55">
@@ -4725,7 +3479,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G56" s="2">
-        <f>_xlfn.DAYS(E56,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H56">
@@ -4767,7 +3521,7 @@
         <v>0.5</v>
       </c>
       <c r="G57" s="2">
-        <f>_xlfn.DAYS(E57,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="H57">
@@ -4816,7 +3570,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G58" s="2">
-        <f>_xlfn.DAYS(E58,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H58">
@@ -4865,7 +3619,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G59" s="2">
-        <f>_xlfn.DAYS(E59,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H59">
@@ -4907,7 +3661,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G60" s="2">
-        <f>_xlfn.DAYS(E60,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H60">
@@ -4949,7 +3703,7 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="2">
-        <f>_xlfn.DAYS(E61,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="H61">
@@ -4998,7 +3752,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G62" s="2">
-        <f>_xlfn.DAYS(E62,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H62">
@@ -5047,7 +3801,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G63" s="2">
-        <f>_xlfn.DAYS(E63,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H63">
@@ -5089,7 +3843,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G64" s="2">
-        <f>_xlfn.DAYS(E64,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H64">
@@ -5131,7 +3885,7 @@
         <v>0.5</v>
       </c>
       <c r="G65" s="2">
-        <f>_xlfn.DAYS(E65,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="H65">
@@ -5180,7 +3934,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G66" s="2">
-        <f>_xlfn.DAYS(E66,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H66">
@@ -5229,7 +3983,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G67" s="2">
-        <f>_xlfn.DAYS(E67,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H67">
@@ -5271,7 +4025,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G68" s="2">
-        <f>_xlfn.DAYS(E68,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H68">
@@ -5313,7 +4067,7 @@
         <v>0.5</v>
       </c>
       <c r="G69" s="2">
-        <f>_xlfn.DAYS(E69,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="H69">
@@ -5362,7 +4116,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G70" s="2">
-        <f>_xlfn.DAYS(E70,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H70">
@@ -5411,7 +4165,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G71" s="2">
-        <f>_xlfn.DAYS(E71,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H71">
@@ -5453,7 +4207,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G72" s="2">
-        <f>_xlfn.DAYS(E72,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H72">
@@ -5495,7 +4249,7 @@
         <v>0.5</v>
       </c>
       <c r="G73" s="2">
-        <f>_xlfn.DAYS(E73,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="H73">
@@ -5544,7 +4298,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G74" s="2">
-        <f>_xlfn.DAYS(E74,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H74">
@@ -5593,7 +4347,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G75" s="2">
-        <f>_xlfn.DAYS(E75,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H75">
@@ -5635,7 +4389,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G76" s="2">
-        <f>_xlfn.DAYS(E76,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H76">
@@ -5677,7 +4431,7 @@
         <v>0.5</v>
       </c>
       <c r="G77" s="2">
-        <f>_xlfn.DAYS(E77,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="H77">
@@ -5726,7 +4480,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G78" s="2">
-        <f>_xlfn.DAYS(E78,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H78">
@@ -5775,7 +4529,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G79" s="2">
-        <f>_xlfn.DAYS(E79,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="H79">
@@ -5817,7 +4571,7 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="G80" s="2">
-        <f>_xlfn.DAYS(E80,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="H80">
@@ -5859,7 +4613,7 @@
         <v>0.5</v>
       </c>
       <c r="G81" s="2">
-        <f>_xlfn.DAYS(E81,$E$54)</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="H81">
@@ -5950,7 +4704,7 @@
         <v>0.5</v>
       </c>
       <c r="G83" s="2">
-        <f t="shared" ref="G83:G109" si="0">_xlfn.DAYS(E83,$E$82)</f>
+        <f t="shared" ref="G83:G133" si="4">_xlfn.DAYS(E83,$E$82)</f>
         <v>10</v>
       </c>
       <c r="H83">
@@ -5992,7 +4746,7 @@
         <v>0.5</v>
       </c>
       <c r="G84" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="H84">
@@ -6034,7 +4788,7 @@
         <v>0.5</v>
       </c>
       <c r="G85" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="H85">
@@ -6076,7 +4830,7 @@
         <v>0.5</v>
       </c>
       <c r="G86" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H86">
@@ -6118,7 +4872,7 @@
         <v>0.5</v>
       </c>
       <c r="G87" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="H87">
@@ -6160,7 +4914,7 @@
         <v>0.5</v>
       </c>
       <c r="G88" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="H88">
@@ -6202,7 +4956,7 @@
         <v>0.5</v>
       </c>
       <c r="G89" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="H89">
@@ -6244,7 +4998,7 @@
         <v>0.5</v>
       </c>
       <c r="G90" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H90">
@@ -6286,7 +5040,7 @@
         <v>0.5</v>
       </c>
       <c r="G91" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="H91">
@@ -6328,7 +5082,7 @@
         <v>0.5</v>
       </c>
       <c r="G92" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="H92">
@@ -6370,7 +5124,7 @@
         <v>0.5</v>
       </c>
       <c r="G93" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="H93">
@@ -6412,7 +5166,7 @@
         <v>0.5</v>
       </c>
       <c r="G94" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H94">
@@ -6454,7 +5208,7 @@
         <v>0.5</v>
       </c>
       <c r="G95" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="H95">
@@ -6496,7 +5250,7 @@
         <v>0.5</v>
       </c>
       <c r="G96" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="H96">
@@ -6538,7 +5292,7 @@
         <v>0.5</v>
       </c>
       <c r="G97" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="H97">
@@ -6580,7 +5334,7 @@
         <v>0.5</v>
       </c>
       <c r="G98" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H98">
@@ -6622,7 +5376,7 @@
         <v>0.5</v>
       </c>
       <c r="G99" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="H99">
@@ -6664,7 +5418,7 @@
         <v>0.5</v>
       </c>
       <c r="G100" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="H100">
@@ -6706,7 +5460,7 @@
         <v>0.5</v>
       </c>
       <c r="G101" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="H101">
@@ -6748,7 +5502,7 @@
         <v>0.5</v>
       </c>
       <c r="G102" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H102">
@@ -6790,7 +5544,7 @@
         <v>0.5</v>
       </c>
       <c r="G103" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="H103">
@@ -6832,7 +5586,7 @@
         <v>0.5</v>
       </c>
       <c r="G104" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="H104">
@@ -6874,7 +5628,7 @@
         <v>0.5</v>
       </c>
       <c r="G105" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="H105">
@@ -6916,7 +5670,7 @@
         <v>0.5</v>
       </c>
       <c r="G106" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H106">
@@ -6958,7 +5712,7 @@
         <v>0.5</v>
       </c>
       <c r="G107" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="H107">
@@ -7000,7 +5754,7 @@
         <v>0.5</v>
       </c>
       <c r="G108" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="H108">
@@ -7042,7 +5796,7 @@
         <v>0.5</v>
       </c>
       <c r="G109" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>92</v>
       </c>
       <c r="H109">
@@ -7065,122 +5819,990 @@
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
+      <c r="A110" t="s">
+        <v>128</v>
+      </c>
+      <c r="B110">
+        <v>240616</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110" t="s">
+        <v>39</v>
+      </c>
+      <c r="G110" s="2">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110" t="s">
+        <v>36</v>
+      </c>
+      <c r="J110">
+        <v>14</v>
+      </c>
+      <c r="K110" s="1">
+        <v>63.529327760134642</v>
+      </c>
+      <c r="L110" s="1">
+        <v>0.21239084816593751</v>
+      </c>
+      <c r="M110" s="1">
+        <v>77</v>
+      </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
+      <c r="A111" t="s">
+        <v>129</v>
+      </c>
+      <c r="B111">
+        <v>240616</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111" t="s">
+        <v>40</v>
+      </c>
+      <c r="G111" s="2">
+        <v>10</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111" t="s">
+        <v>36</v>
+      </c>
+      <c r="J111">
+        <v>14</v>
+      </c>
+      <c r="K111" s="1">
+        <v>60.71622487204445</v>
+      </c>
+      <c r="L111" s="1">
+        <v>0.3692459590258006</v>
+      </c>
+      <c r="M111" s="1">
+        <v>77</v>
+      </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-    </row>
-    <row r="113" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-    </row>
-    <row r="114" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-    </row>
-    <row r="115" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-    </row>
-    <row r="116" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-    </row>
-    <row r="117" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-    </row>
-    <row r="118" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-    </row>
-    <row r="119" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-    </row>
-    <row r="120" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-    </row>
-    <row r="121" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-    </row>
-    <row r="122" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-    </row>
-    <row r="123" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-    </row>
-    <row r="124" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-    </row>
-    <row r="125" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-    </row>
-    <row r="126" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-    </row>
-    <row r="127" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-    </row>
-    <row r="128" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-    </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-    </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-    </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-    </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-    </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-    </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
-    </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
-    </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
-    </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-    </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>130</v>
+      </c>
+      <c r="B112">
+        <v>240616</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
+        <v>40</v>
+      </c>
+      <c r="G112" s="2">
+        <v>31</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112" t="s">
+        <v>36</v>
+      </c>
+      <c r="J112">
+        <v>14</v>
+      </c>
+      <c r="K112" s="1">
+        <v>58.293889076698683</v>
+      </c>
+      <c r="L112" s="1">
+        <v>0.42985966628108901</v>
+      </c>
+      <c r="M112" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>131</v>
+      </c>
+      <c r="B113">
+        <v>240616</v>
+      </c>
+      <c r="C113">
+        <v>3</v>
+      </c>
+      <c r="D113" t="s">
+        <v>41</v>
+      </c>
+      <c r="G113" s="2">
+        <v>92</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113" t="s">
+        <v>36</v>
+      </c>
+      <c r="J113">
+        <v>14</v>
+      </c>
+      <c r="K113" s="1">
+        <v>56.367365291501734</v>
+      </c>
+      <c r="L113" s="1">
+        <v>0.48604363877175832</v>
+      </c>
+      <c r="M113" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>132</v>
+      </c>
+      <c r="B114">
+        <v>240616</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114" t="s">
+        <v>39</v>
+      </c>
+      <c r="G114" s="2">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114" t="s">
+        <v>37</v>
+      </c>
+      <c r="J114">
+        <v>14</v>
+      </c>
+      <c r="K114" s="1">
+        <v>89.31155228787388</v>
+      </c>
+      <c r="L114" s="1">
+        <v>0.31697292948060768</v>
+      </c>
+      <c r="M114" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>133</v>
+      </c>
+      <c r="B115">
+        <v>240616</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115" t="s">
+        <v>40</v>
+      </c>
+      <c r="G115" s="2">
+        <v>10</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115" t="s">
+        <v>37</v>
+      </c>
+      <c r="J115">
+        <v>14</v>
+      </c>
+      <c r="K115" s="1">
+        <v>67.394980720617056</v>
+      </c>
+      <c r="L115" s="1">
+        <v>1.1080665489943649</v>
+      </c>
+      <c r="M115" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>134</v>
+      </c>
+      <c r="B116">
+        <v>240616</v>
+      </c>
+      <c r="C116">
+        <v>2</v>
+      </c>
+      <c r="D116" t="s">
+        <v>40</v>
+      </c>
+      <c r="G116" s="2">
+        <v>31</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116" t="s">
+        <v>37</v>
+      </c>
+      <c r="J116">
+        <v>14</v>
+      </c>
+      <c r="K116" s="1">
+        <v>62.034538585469846</v>
+      </c>
+      <c r="L116" s="1">
+        <v>0.25128579827236686</v>
+      </c>
+      <c r="M116" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>135</v>
+      </c>
+      <c r="B117">
+        <v>240616</v>
+      </c>
+      <c r="C117">
+        <v>3</v>
+      </c>
+      <c r="D117" t="s">
+        <v>41</v>
+      </c>
+      <c r="G117" s="2">
+        <v>92</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117" t="s">
+        <v>37</v>
+      </c>
+      <c r="J117">
+        <v>14</v>
+      </c>
+      <c r="K117" s="1">
+        <v>60.250875887942904</v>
+      </c>
+      <c r="L117" s="1">
+        <v>0.11934970347147902</v>
+      </c>
+      <c r="M117" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>136</v>
+      </c>
+      <c r="B118">
+        <v>240616</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118" t="s">
+        <v>39</v>
+      </c>
+      <c r="G118" s="2">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>2</v>
+      </c>
+      <c r="I118" t="s">
+        <v>37</v>
+      </c>
+      <c r="J118">
+        <v>14</v>
+      </c>
+      <c r="K118" s="1">
+        <v>91.546908130239785</v>
+      </c>
+      <c r="L118" s="1">
+        <v>0.67046230039043164</v>
+      </c>
+      <c r="M118" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>137</v>
+      </c>
+      <c r="B119">
+        <v>240616</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119" t="s">
+        <v>40</v>
+      </c>
+      <c r="G119" s="2">
+        <v>10</v>
+      </c>
+      <c r="H119">
+        <v>2</v>
+      </c>
+      <c r="I119" t="s">
+        <v>37</v>
+      </c>
+      <c r="J119">
+        <v>14</v>
+      </c>
+      <c r="K119" s="1">
+        <v>65.790944831851675</v>
+      </c>
+      <c r="L119" s="1">
+        <v>0.47715952751879548</v>
+      </c>
+      <c r="M119" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>138</v>
+      </c>
+      <c r="B120">
+        <v>240616</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+      <c r="D120" t="s">
+        <v>40</v>
+      </c>
+      <c r="G120" s="2">
+        <v>31</v>
+      </c>
+      <c r="H120">
+        <v>2</v>
+      </c>
+      <c r="I120" t="s">
+        <v>37</v>
+      </c>
+      <c r="J120">
+        <v>14</v>
+      </c>
+      <c r="K120" s="1">
+        <v>61.728857875822996</v>
+      </c>
+      <c r="L120" s="1">
+        <v>0.20961396762245141</v>
+      </c>
+      <c r="M120" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>139</v>
+      </c>
+      <c r="B121">
+        <v>240616</v>
+      </c>
+      <c r="C121">
+        <v>3</v>
+      </c>
+      <c r="D121" t="s">
+        <v>41</v>
+      </c>
+      <c r="G121" s="2">
+        <v>92</v>
+      </c>
+      <c r="H121">
+        <v>2</v>
+      </c>
+      <c r="I121" t="s">
+        <v>37</v>
+      </c>
+      <c r="J121">
+        <v>14</v>
+      </c>
+      <c r="K121" s="1">
+        <v>58.848526240593976</v>
+      </c>
+      <c r="L121" s="1">
+        <v>0.63225435413615416</v>
+      </c>
+      <c r="M121" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>140</v>
+      </c>
+      <c r="B122">
+        <v>240616</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122" t="s">
+        <v>39</v>
+      </c>
+      <c r="G122" s="2">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>3</v>
+      </c>
+      <c r="I122" t="s">
+        <v>37</v>
+      </c>
+      <c r="J122">
+        <v>14</v>
+      </c>
+      <c r="K122" s="1">
+        <v>70.804738739564314</v>
+      </c>
+      <c r="L122" s="1">
+        <v>0.65258261943905616</v>
+      </c>
+      <c r="M122" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>141</v>
+      </c>
+      <c r="B123">
+        <v>240616</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123" t="s">
+        <v>40</v>
+      </c>
+      <c r="G123" s="2">
+        <v>10</v>
+      </c>
+      <c r="H123">
+        <v>3</v>
+      </c>
+      <c r="I123" t="s">
+        <v>37</v>
+      </c>
+      <c r="J123">
+        <v>14</v>
+      </c>
+      <c r="K123" s="1">
+        <v>63.079735513643755</v>
+      </c>
+      <c r="L123" s="1">
+        <v>1.2737020029419943</v>
+      </c>
+      <c r="M123" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>142</v>
+      </c>
+      <c r="B124">
+        <v>240616</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+      <c r="D124" t="s">
+        <v>40</v>
+      </c>
+      <c r="G124" s="2">
+        <v>31</v>
+      </c>
+      <c r="H124">
+        <v>3</v>
+      </c>
+      <c r="I124" t="s">
+        <v>37</v>
+      </c>
+      <c r="J124">
+        <v>14</v>
+      </c>
+      <c r="K124" s="1">
+        <v>61.574441847238511</v>
+      </c>
+      <c r="L124" s="1">
+        <v>0.53445156878411459</v>
+      </c>
+      <c r="M124" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>143</v>
+      </c>
+      <c r="B125">
+        <v>240616</v>
+      </c>
+      <c r="C125">
+        <v>3</v>
+      </c>
+      <c r="D125" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" s="2">
+        <v>92</v>
+      </c>
+      <c r="H125">
+        <v>3</v>
+      </c>
+      <c r="I125" t="s">
+        <v>37</v>
+      </c>
+      <c r="J125">
+        <v>14</v>
+      </c>
+      <c r="K125" s="1">
+        <v>59.598546950861497</v>
+      </c>
+      <c r="L125" s="1">
+        <v>0.34592170120196186</v>
+      </c>
+      <c r="M125" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>140</v>
+      </c>
+      <c r="B126">
+        <v>240616</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>39</v>
+      </c>
+      <c r="G126" s="2">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>4</v>
+      </c>
+      <c r="I126" t="s">
+        <v>37</v>
+      </c>
+      <c r="J126">
+        <v>14</v>
+      </c>
+      <c r="K126" s="1">
+        <v>75.443162721305399</v>
+      </c>
+      <c r="L126" s="1">
+        <v>0.68755142886196541</v>
+      </c>
+      <c r="M126" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>141</v>
+      </c>
+      <c r="B127">
+        <v>240616</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127" t="s">
+        <v>40</v>
+      </c>
+      <c r="G127" s="2">
+        <v>10</v>
+      </c>
+      <c r="H127">
+        <v>4</v>
+      </c>
+      <c r="I127" t="s">
+        <v>37</v>
+      </c>
+      <c r="J127">
+        <v>14</v>
+      </c>
+      <c r="K127" s="1">
+        <v>65.888665366808041</v>
+      </c>
+      <c r="L127" s="1">
+        <v>0.54138852676341487</v>
+      </c>
+      <c r="M127" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>142</v>
+      </c>
+      <c r="B128">
+        <v>240616</v>
+      </c>
+      <c r="C128">
+        <v>2</v>
+      </c>
+      <c r="D128" t="s">
+        <v>40</v>
+      </c>
+      <c r="G128" s="2">
+        <v>31</v>
+      </c>
+      <c r="H128">
+        <v>4</v>
+      </c>
+      <c r="I128" t="s">
+        <v>37</v>
+      </c>
+      <c r="J128">
+        <v>14</v>
+      </c>
+      <c r="K128" s="1">
+        <v>61.253744731887416</v>
+      </c>
+      <c r="L128" s="1">
+        <v>1.0990135066643572</v>
+      </c>
+      <c r="M128" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>143</v>
+      </c>
+      <c r="B129">
+        <v>240616</v>
+      </c>
+      <c r="C129">
+        <v>3</v>
+      </c>
+      <c r="D129" t="s">
+        <v>41</v>
+      </c>
+      <c r="G129" s="2">
+        <v>92</v>
+      </c>
+      <c r="H129">
+        <v>4</v>
+      </c>
+      <c r="I129" t="s">
+        <v>37</v>
+      </c>
+      <c r="J129">
+        <v>14</v>
+      </c>
+      <c r="K129" s="1">
+        <v>58.779670657813334</v>
+      </c>
+      <c r="L129" s="1">
+        <v>0.44468625319162769</v>
+      </c>
+      <c r="M129" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>144</v>
+      </c>
+      <c r="B130">
+        <v>240616</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130" t="s">
+        <v>39</v>
+      </c>
+      <c r="G130" s="2">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>5</v>
+      </c>
+      <c r="I130" t="s">
+        <v>37</v>
+      </c>
+      <c r="J130">
+        <v>14</v>
+      </c>
+      <c r="K130" s="1">
+        <v>74.987078065220743</v>
+      </c>
+      <c r="L130" s="1">
+        <v>0.89342380607061378</v>
+      </c>
+      <c r="M130" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>145</v>
+      </c>
+      <c r="B131">
+        <v>240616</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131" t="s">
+        <v>40</v>
+      </c>
+      <c r="G131" s="2">
+        <v>10</v>
+      </c>
+      <c r="H131">
+        <v>5</v>
+      </c>
+      <c r="I131" t="s">
+        <v>37</v>
+      </c>
+      <c r="J131">
+        <v>14</v>
+      </c>
+      <c r="K131" s="1">
+        <v>64.601892880035564</v>
+      </c>
+      <c r="L131" s="1">
+        <v>0.55214676054786438</v>
+      </c>
+      <c r="M131" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>146</v>
+      </c>
+      <c r="B132">
+        <v>240616</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132" t="s">
+        <v>40</v>
+      </c>
+      <c r="G132" s="2">
+        <v>31</v>
+      </c>
+      <c r="H132">
+        <v>5</v>
+      </c>
+      <c r="I132" t="s">
+        <v>37</v>
+      </c>
+      <c r="J132">
+        <v>14</v>
+      </c>
+      <c r="K132" s="1">
+        <v>60.97755425569693</v>
+      </c>
+      <c r="L132" s="1">
+        <v>1.0718552942122948</v>
+      </c>
+      <c r="M132" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>147</v>
+      </c>
+      <c r="B133">
+        <v>240616</v>
+      </c>
+      <c r="C133">
+        <v>3</v>
+      </c>
+      <c r="D133" t="s">
+        <v>41</v>
+      </c>
+      <c r="G133" s="2">
+        <v>92</v>
+      </c>
+      <c r="H133">
+        <v>5</v>
+      </c>
+      <c r="I133" t="s">
+        <v>37</v>
+      </c>
+      <c r="J133">
+        <v>14</v>
+      </c>
+      <c r="K133" s="1">
+        <v>59.010623038765715</v>
+      </c>
+      <c r="L133" s="1">
+        <v>0.74937461678691286</v>
+      </c>
+      <c r="M133" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>148</v>
+      </c>
+      <c r="B134">
+        <v>240616</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134" t="s">
+        <v>39</v>
+      </c>
+      <c r="G134" s="2">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>6</v>
+      </c>
+      <c r="I134" t="s">
+        <v>37</v>
+      </c>
+      <c r="J134">
+        <v>14</v>
+      </c>
+      <c r="K134" s="1">
+        <v>79.700285030854886</v>
+      </c>
+      <c r="L134" s="1">
+        <v>0.48304697562671345</v>
+      </c>
+      <c r="M134" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>149</v>
+      </c>
+      <c r="B135">
+        <v>240616</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>40</v>
+      </c>
+      <c r="G135" s="2">
+        <v>10</v>
+      </c>
+      <c r="H135">
+        <v>6</v>
+      </c>
+      <c r="I135" t="s">
+        <v>37</v>
+      </c>
+      <c r="J135">
+        <v>14</v>
+      </c>
+      <c r="K135" s="1">
+        <v>65.921967878751332</v>
+      </c>
+      <c r="L135" s="1">
+        <v>1.3860420546907748</v>
+      </c>
+      <c r="M135" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>150</v>
+      </c>
+      <c r="B136">
+        <v>240616</v>
+      </c>
+      <c r="C136">
+        <v>2</v>
+      </c>
+      <c r="D136" t="s">
+        <v>40</v>
+      </c>
+      <c r="G136" s="2">
+        <v>31</v>
+      </c>
+      <c r="H136">
+        <v>6</v>
+      </c>
+      <c r="I136" t="s">
+        <v>37</v>
+      </c>
+      <c r="J136">
+        <v>14</v>
+      </c>
+      <c r="K136" s="1">
+        <v>62.022830877672583</v>
+      </c>
+      <c r="L136" s="1">
+        <v>0.48930854480167424</v>
+      </c>
+      <c r="M136" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>151</v>
+      </c>
+      <c r="B137">
+        <v>240616</v>
+      </c>
+      <c r="C137">
+        <v>3</v>
+      </c>
+      <c r="D137" t="s">
+        <v>41</v>
+      </c>
+      <c r="G137" s="2">
+        <v>92</v>
+      </c>
+      <c r="H137">
+        <v>6</v>
+      </c>
+      <c r="I137" t="s">
+        <v>37</v>
+      </c>
+      <c r="J137">
+        <v>14</v>
+      </c>
+      <c r="K137" s="1">
+        <v>58.992625915428789</v>
+      </c>
+      <c r="L137" s="1">
+        <v>0.46316020277981762</v>
+      </c>
+      <c r="M137" s="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
     </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
     </row>
@@ -7191,6 +6813,5 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>